--- a/artfynd/A 42236-2021 artfynd.xlsx
+++ b/artfynd/A 42236-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42236-2021 artfynd.xlsx
+++ b/artfynd/A 42236-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>909841</v>
+        <v>343430</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535292.8740809535</v>
+        <v>535004</v>
       </c>
       <c r="R2" t="n">
-        <v>7046303.925215454</v>
+        <v>7046441</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>343430</v>
+        <v>909841</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535004.2130807961</v>
+        <v>535293</v>
       </c>
       <c r="R3" t="n">
-        <v>7046441.217031579</v>
+        <v>7046304</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1997503</v>
+        <v>909842</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535292.8988178769</v>
+        <v>535277</v>
       </c>
       <c r="R4" t="n">
-        <v>7046301.695575478</v>
+        <v>7046322</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2072925</v>
+        <v>488254</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535274.8054211991</v>
+        <v>535065</v>
       </c>
       <c r="R5" t="n">
-        <v>7046322.456020668</v>
+        <v>7046438</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1569092</v>
+        <v>1871761</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535147.3262202182</v>
+        <v>535047</v>
       </c>
       <c r="R6" t="n">
-        <v>7046421.834809698</v>
+        <v>7046518</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4051492</v>
+        <v>1980727</v>
       </c>
       <c r="B7" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535104.2301852291</v>
+        <v>534997</v>
       </c>
       <c r="R7" t="n">
-        <v>7046442.319235885</v>
+        <v>7046529</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>909842</v>
+        <v>1997502</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535276.601398465</v>
+        <v>535292</v>
       </c>
       <c r="R8" t="n">
-        <v>7046321.583976455</v>
+        <v>7046184</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>488254</v>
+        <v>1997503</v>
       </c>
       <c r="B9" t="n">
-        <v>92505</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2412</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535065.4284993132</v>
+        <v>535293</v>
       </c>
       <c r="R9" t="n">
-        <v>7046437.877595372</v>
+        <v>7046302</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1937572</v>
+        <v>2072925</v>
       </c>
       <c r="B10" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535291.6147473558</v>
+        <v>535275</v>
       </c>
       <c r="R10" t="n">
-        <v>7046175.911634115</v>
+        <v>7046322</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,19 +1551,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1997502</v>
+        <v>1937572</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535291.525698615</v>
+        <v>535292</v>
       </c>
       <c r="R11" t="n">
-        <v>7046183.938647259</v>
+        <v>7046176</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,19 +1652,9 @@
           <t>2012-09-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2012-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,6 +1678,107 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4051492</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Recksjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>535104</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7046442</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2012-09-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2012-09-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 42236-2021 artfynd.xlsx
+++ b/artfynd/A 42236-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/343430</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/909841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/909842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/488254</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1871761</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1980727</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2072925</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937572</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,8 +1838,26 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4051492</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>